--- a/05_Figures/F06_prediction/proteins/acute/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/acute/d_1rm_ext/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -131,139 +131,163 @@
     <t xml:space="preserve">RCSD1</t>
   </si>
   <si>
+    <t xml:space="preserve">TACC2</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHORDC1</t>
   </si>
   <si>
-    <t xml:space="preserve">TACC2</t>
+    <t xml:space="preserve">MYOF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS15L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDIA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZYX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANK2</t>
   </si>
   <si>
     <t xml:space="preserve">ATP1B1</t>
   </si>
   <si>
-    <t xml:space="preserve">EPS15L1</t>
+    <t xml:space="preserve">DAG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSTN</t>
   </si>
   <si>
     <t xml:space="preserve">GLRX</t>
   </si>
   <si>
-    <t xml:space="preserve">MYOF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDIA6</t>
+    <t xml:space="preserve">GSTO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCL3</t>
   </si>
   <si>
     <t xml:space="preserve">RAB12</t>
   </si>
   <si>
-    <t xml:space="preserve">SH3BGRL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZYX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSTN</t>
+    <t xml:space="preserve">CLUH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSRP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIABLO</t>
   </si>
   <si>
     <t xml:space="preserve">NGLY1</t>
   </si>
   <si>
-    <t xml:space="preserve">PDCL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSRP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIABLO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTO1</t>
-  </si>
-  <si>
     <t xml:space="preserve">PRPS1</t>
   </si>
   <si>
     <t xml:space="preserve">RUVBL2</t>
   </si>
   <si>
-    <t xml:space="preserve">CLUH</t>
-  </si>
-  <si>
     <t xml:space="preserve">DCTN3</t>
   </si>
   <si>
+    <t xml:space="preserve">SHOC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIC1</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPS24</t>
   </si>
   <si>
+    <t xml:space="preserve">CAB39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPNE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIST2H2BE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGST2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLN1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ATP5PD</t>
   </si>
   <si>
-    <t xml:space="preserve">CAB39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGST2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHOC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIST2H2BE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPNE3</t>
+    <t xml:space="preserve">CAP1</t>
   </si>
   <si>
     <t xml:space="preserve">GSTZ1</t>
   </si>
   <si>
+    <t xml:space="preserve">HPCAL1</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPIL1</t>
   </si>
   <si>
+    <t xml:space="preserve">TAGLN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAMPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGPEP1</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRELP</t>
   </si>
   <si>
-    <t xml:space="preserve">CAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPCAL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGPEP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAGLN</t>
+    <t xml:space="preserve">TGM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMED1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2D1</t>
   </si>
   <si>
     <t xml:space="preserve">ADIRF</t>
   </si>
   <si>
-    <t xml:space="preserve">CACNB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP1</t>
+    <t xml:space="preserve">CLASP2</t>
   </si>
   <si>
     <t xml:space="preserve">DBT</t>
@@ -272,343 +296,286 @@
     <t xml:space="preserve">ENO2</t>
   </si>
   <si>
-    <t xml:space="preserve">MYH11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAMPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMED1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2D1</t>
+    <t xml:space="preserve">LAMP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSBPL1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCBP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHYKPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC1A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOMM40</t>
   </si>
   <si>
     <t xml:space="preserve">ABCF2</t>
   </si>
   <si>
-    <t xml:space="preserve">ACP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLASP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL18A1</t>
+    <t xml:space="preserve">ACO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ART3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCAP29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLMH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOLA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPNS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDV3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLTB</t>
   </si>
   <si>
     <t xml:space="preserve">COPS2</t>
   </si>
   <si>
+    <t xml:space="preserve">COPS5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ10B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIP1</t>
+  </si>
+  <si>
     <t xml:space="preserve">DHCR24</t>
   </si>
   <si>
-    <t xml:space="preserve">FLNA</t>
+    <t xml:space="preserve">DNPEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF4E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELOB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPHX2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAHD2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBLN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDXR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FKBP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLOT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FNTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRSF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H4C1</t>
   </si>
   <si>
     <t xml:space="preserve">HAGH</t>
   </si>
   <si>
+    <t xml:space="preserve">HBS1L</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSD17B4</t>
   </si>
   <si>
+    <t xml:space="preserve">IARS1</t>
+  </si>
+  <si>
     <t xml:space="preserve">IBA57</t>
   </si>
   <si>
-    <t xml:space="preserve">LAMP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSBPL1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCBP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME1</t>
+    <t xml:space="preserve">IDI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICU2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MT-ATP8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYOM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NTPCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUBPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBSCN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAFAH1B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARVB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCD6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2R5A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP5C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PYGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAP1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDH11</t>
   </si>
   <si>
     <t xml:space="preserve">RDH13</t>
   </si>
   <si>
-    <t xml:space="preserve">S100A6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SBDS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC44A2</t>
+    <t xml:space="preserve">RSU1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIRT5</t>
   </si>
   <si>
     <t xml:space="preserve">SOD2</t>
   </si>
   <si>
+    <t xml:space="preserve">SRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SURF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYPL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TKT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRMT10C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCHL3</t>
+  </si>
+  <si>
     <t xml:space="preserve">UGGT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH9A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ART3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1E1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLMH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOLA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPNS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCT5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDV3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ10B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHODH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNPEP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF4E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELOB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPHX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FABP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAHD2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FBLN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDXR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FKBP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FNTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GFM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRSF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H4C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBS1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MICU2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MT-ATP8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYOM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NANS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NTPCR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUBPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBSCN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAFAH1B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARVB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMPCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2R5A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP5C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PYGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAP1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRAS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSU1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SARS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEPTIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIRT5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC1A4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SURF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYPL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TKT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOMM40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRMT10C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCHL3</t>
   </si>
   <si>
     <t xml:space="preserve">UQCRH</t>
@@ -1001,16 +968,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.580251030462029</v>
+        <v>-0.683522698609135</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.165198638627858</v>
+        <v>-0.224670148533886</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1034,29 +1001,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.580251030462029</v>
+        <v>-0.683522698609135</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.165198638627858</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.497512437810945</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.54228855721393</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.696264502728835</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.708119863277053</v>
-      </c>
+        <v>-0.224670148533886</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1080,2206 +1039,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-2.12624723294987</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.496843344813676</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.614078905614006</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1.8379903110464</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.041257487035893</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-1.23424326199685</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.736379344963804</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.237237327789473</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.114606155880873</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.720316850657762</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.577032856011656</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.777272335122901</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.66563341868324</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.173891041719283</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.431535839007003</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.195614289725267</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.45224995968469</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.314128795697344</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-1.26065160667662</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.22524898367289</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.42024065380994</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.0845281216269195</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.622066614689905</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.234545783923668</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.887338458665106</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-1.63349707967734</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.0859764763204098</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.486971289810972</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-1.42101732588752</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.36021933991106</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-1.5758452703558</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-1.00697979179072</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.77744145014448</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-2.84014224800659</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.402559021005739</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.439252996159392</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.190265075628913</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.00517740407188</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.482682133829711</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.261931079277335</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.392855305803516</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.474861566498973</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.536945177994461</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-2.95702748655575</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.132311885590171</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.23982990247522</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.576219309252065</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.470465834345318</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.464394133369167</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.284139045361148</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.292883678327363</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.139188352641683</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.795594321152762</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-1.53308232978719</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-1.97956155245965</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.6533696517603</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.46476405006318</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.665481234995571</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.0219507793903395</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.37963584744399</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.702737481210266</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.161714658228732</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.626476179948009</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.493239726474221</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.075657027926207</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.213859126265478</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.674889772635473</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.482925451335378</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-1.62798841963108</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-1.8739427930524</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.902295032836185</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.875363367278708</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.0326140172761995</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-2.14383991562454</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.180215268909705</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-1.25872655933375</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-1.21284235126206</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.396221773247059</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.898183451313184</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.961995266179543</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.324986536939644</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.446814504260286</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.993106049505386</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-1.07571354281418</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-1.18100544562887</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.105700476530795</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-1.14347348988836</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.24005282527979</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-1.81681602341798</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-1.19940962446857</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-1.25575276323367</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.135223896807888</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.131330989964259</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.133154046065925</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.679972461057915</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.934408359094548</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0.013672479874926</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.146434148426884</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.362405732763761</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-2.79671653557875</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.830383792098616</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.302174814722146</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-2.93485385004911</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.95220965381467</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-1.06462767646726</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.315712026745694</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.60210460992749</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-1.0155969210431</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.0197726828413143</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.419919358918169</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>0.0278826079900526</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-1.48261111682102</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.883782787826642</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.0987572361742026</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>0.108917610796381</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-1.09263656376311</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.62680257235732</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-1.8745814600014</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.684253091668115</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.65250429507949</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-1.02394537285388</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-1.21799544666118</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-1.11125593565159</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0.413430775301248</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-1.51825571776429</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.626396208774913</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-2.24918749356849</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>0.3175490788177</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.278496906707498</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.119530645349951</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.267659664728465</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.497222732507896</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.794608324601807</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-1.34715010588161</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.288028233498839</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.199611698827626</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-1.34824678963966</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.34920336110446</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.362657544554952</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-1.42750960452425</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0.0994800065332276</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-1.36935240228109</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.726155110047886</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.246127802870606</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.92643247409276</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.812973132172272</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.28253550063153</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.774924661089327</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.544817404460562</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.673090863026484</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.946232682866909</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-1.19289982693362</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-2.26493682433361</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.249089481431491</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.417763040693109</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.362813147476853</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>0.501512275166363</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.95064701622287</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.504811815505705</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>0.156899572378784</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.249580808349936</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-1.60144747082717</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-1.19242121525005</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>0.104115962440374</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-1.30551340797766</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>0.401693832690487</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.912850411041195</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-1.01875527622378</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>0.428169410519492</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-1.49675926388279</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.73199549008398</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-1.37977650275821</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-1.81176732153957</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.69943404775351</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-1.12103788575802</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.739950365645556</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.0335183866985613</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-1.27572350114115</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.261337101943325</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.727557770873647</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>0.148415891921684</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.373726379727976</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.446885451256271</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.543270614200011</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-1.19958344206552</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.382645126826458</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>0.107780413684324</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-1.16629076516623</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-1.69125151006092</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.700489000408566</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.540443393240715</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.112244647171163</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.196971968211209</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-1.22557336524183</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.184443400280723</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.346472201400268</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.0130133935717009</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>0.112092721930637</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.143025648964878</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.920005077382299</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3322,7 +1081,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4889789852916</v>
+        <v>9.73043768548537</v>
       </c>
     </row>
     <row r="3">
@@ -3339,7 +1098,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>3.04028199013808</v>
+        <v>3.23988468265131</v>
       </c>
     </row>
     <row r="4">
@@ -3356,7 +1115,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>11.1296472380997</v>
+        <v>11.2351937361371</v>
       </c>
     </row>
     <row r="5">
@@ -3373,7 +1132,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>2.66781280348916</v>
+        <v>3.05934399528271</v>
       </c>
     </row>
     <row r="6">
@@ -3390,7 +1149,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>12.057127088022</v>
+        <v>11.9133172319936</v>
       </c>
     </row>
     <row r="7">
@@ -3407,7 +1166,7 @@
         <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>4.19937929549138</v>
+        <v>4.30985600827861</v>
       </c>
     </row>
     <row r="8">
@@ -3424,7 +1183,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>9.81313089756976</v>
+        <v>15.285870932991</v>
       </c>
     </row>
     <row r="9">
@@ -3441,7 +1200,7 @@
         <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>8.2902939923902</v>
+        <v>8.39014558045169</v>
       </c>
     </row>
     <row r="10">
@@ -3458,7 +1217,7 @@
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>13.2973112144018</v>
+        <v>13.1648734507765</v>
       </c>
     </row>
     <row r="11">
@@ -3475,7 +1234,7 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>9.23794394941699</v>
+        <v>9.23619390953763</v>
       </c>
     </row>
     <row r="12">
@@ -3492,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>10.4092673621094</v>
+        <v>9.77998435813972</v>
       </c>
     </row>
     <row r="13">
@@ -3509,7 +1268,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>8.94209446662067</v>
+        <v>8.71932573419716</v>
       </c>
     </row>
     <row r="14">
@@ -3526,7 +1285,7 @@
         <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>10.4956089491549</v>
+        <v>10.2066459605331</v>
       </c>
     </row>
     <row r="15">
@@ -3543,7 +1302,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>6.54811167360689</v>
+        <v>6.58776536810086</v>
       </c>
     </row>
   </sheetData>
@@ -3585,10 +1344,10 @@
         <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="3">
@@ -3619,10 +1378,10 @@
         <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="5">
@@ -3670,10 +1429,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="8">
@@ -3687,10 +1446,10 @@
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="9">
@@ -3704,10 +1463,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="10">
@@ -3721,10 +1480,10 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="11">
@@ -3738,10 +1497,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.857142857142857</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="12">
@@ -3755,10 +1514,10 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.857142857142857</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="13">
@@ -3772,10 +1531,10 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="14">
@@ -3789,10 +1548,10 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="15">
@@ -3806,10 +1565,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="16">
@@ -3823,10 +1582,10 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="17">
@@ -3840,10 +1599,10 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="18">
@@ -3857,10 +1616,10 @@
         <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="19">
@@ -3874,10 +1633,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="20">
@@ -3891,10 +1650,10 @@
         <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="21">
@@ -3908,10 +1667,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="22">
@@ -3925,10 +1684,10 @@
         <v>57</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="23">
@@ -3942,10 +1701,10 @@
         <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="24">
@@ -4044,10 +1803,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="30">
@@ -4061,10 +1820,10 @@
         <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="31">
@@ -4078,10 +1837,10 @@
         <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="32">
@@ -4095,10 +1854,10 @@
         <v>67</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="33">
@@ -4197,10 +1956,10 @@
         <v>73</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="39">
@@ -4214,10 +1973,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="40">
@@ -4231,10 +1990,10 @@
         <v>75</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="41">
@@ -4282,10 +2041,10 @@
         <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="44">
@@ -4299,10 +2058,10 @@
         <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="45">
@@ -4469,10 +2228,10 @@
         <v>89</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="55">
@@ -4741,10 +2500,10 @@
         <v>105</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="71">
@@ -4758,10 +2517,10 @@
         <v>106</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="72">
@@ -4775,10 +2534,10 @@
         <v>107</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="73">
@@ -4792,10 +2551,10 @@
         <v>108</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="74">
@@ -4809,10 +2568,10 @@
         <v>109</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="75">
@@ -4826,10 +2585,10 @@
         <v>110</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="76">
@@ -4843,10 +2602,10 @@
         <v>111</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="77">
@@ -4860,10 +2619,10 @@
         <v>112</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="78">
@@ -6155,193 +3914,6 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="s">
-        <v>189</v>
-      </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="s">
-        <v>190</v>
-      </c>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="s">
-        <v>191</v>
-      </c>
-      <c r="D156" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="s">
-        <v>192</v>
-      </c>
-      <c r="D157" t="n">
-        <v>1</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="s">
-        <v>193</v>
-      </c>
-      <c r="D158" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="s">
-        <v>194</v>
-      </c>
-      <c r="D159" t="n">
-        <v>1</v>
-      </c>
-      <c r="E159" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="s">
-        <v>195</v>
-      </c>
-      <c r="D160" t="n">
-        <v>1</v>
-      </c>
-      <c r="E160" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="s">
-        <v>196</v>
-      </c>
-      <c r="D161" t="n">
-        <v>1</v>
-      </c>
-      <c r="E161" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="s">
-        <v>197</v>
-      </c>
-      <c r="D162" t="n">
-        <v>1</v>
-      </c>
-      <c r="E162" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="s">
-        <v>198</v>
-      </c>
-      <c r="D163" t="n">
-        <v>1</v>
-      </c>
-      <c r="E163" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="s">
-        <v>199</v>
-      </c>
-      <c r="D164" t="n">
-        <v>1</v>
-      </c>
-      <c r="E164" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/acute/d_1rm_ext/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/acute/d_1rm_ext/spls/c_data/results.xlsx
@@ -1004,7 +1004,7 @@
         <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.683522698609135</v>
@@ -1012,10 +1012,18 @@
       <c r="I3" t="n">
         <v>-0.224670148533886</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.537313432835821</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.582089552238806</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.699407051563432</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.719698468517711</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1039,6 +1047,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.99251954381057</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.575918580006978</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.83515891344425</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.87688428023809</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.00705096893119739</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.23344266675882</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.932111768255691</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.0719392052974179</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.19595063613172</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.762876031295022</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.587115481468484</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.816202087632486</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.78807294287461</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.17965485081654</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.685509775189979</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.265243159947114</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.430974425266986</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.38973187390726</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.2979428880286</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.48384632204186</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-2.05318063588998</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0742343409422526</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.540788615428518</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.478977503587251</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.953524978550331</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-1.52858310479125</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0653950409865399</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.618048134965788</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-1.39836083263168</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.362655580376057</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-1.25939873428002</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.899034723857665</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.44044074953765</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-2.99955433421821</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.338182815344159</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.441473064516788</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.26001505185133</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.02971785963914</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.00399419698316505</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.0848602378620262</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.0558558783163507</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.403368274860324</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.480067661570126</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-3.07715723940892</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.0592058923008643</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.210760961147855</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.562739933987383</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.681219861172579</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.340740162194931</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.12581119070272</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.389538454792232</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.16774475625909</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.865303697172341</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.730599825624025</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-1.86172989035776</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.642427525845488</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.46531135478319</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.611183460572089</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.0626967298475144</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.407380154796877</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.764471938109508</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.0427408794940786</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.431682856547987</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.690871566046776</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.0607764241249271</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.143226603882274</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-1.00459674256834</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.285056953864662</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.5388458174148</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-2.93551185098827</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-1.09180396968031</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.22248404225774</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.00774519029028453</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-1.92665105482857</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.338976257218634</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1.2155478700749</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1.84941932490699</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.479599826068539</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.782500229470405</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.88152235246082</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.374637098711061</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.440106276961568</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.12797071871104</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.072340723888</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-1.01591485863726</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.0401977420935541</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.14273446358556</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.176557335361031</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-1.7991593925661</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-1.06239439139784</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-1.19716838926801</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.141094251154892</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.0332545604714605</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.111204673329762</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.00510821067658</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.960491695234998</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.0802873163359141</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.148512585766757</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.265631084390278</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-2.68986958713047</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.829469839458448</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.322171314030434</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-2.86036480059195</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.639285783825902</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.971194870503287</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.142677424106449</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.434029813644515</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.884306680403268</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.00749503414739128</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.765006947917514</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.172796384074901</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-1.49030593941703</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.903971625368416</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.0995313327614247</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.078915340895998</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.13469221700494</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.555578283479347</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1.99898516906484</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.616001571235527</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.56162623521866</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.921595163535234</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.879641665082968</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-1.19517109134103</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.350055221560122</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1.63982660079417</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.590561396270106</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-1.91887763228022</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.276519860126433</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.265790864056476</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.172414335478733</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.196491077177508</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.346986187657402</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.826477341288869</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.23307890244094</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.296824786111602</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.0837156706503641</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.12714539549258</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.348104040166626</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.359343880679656</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-1.3060566868663</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.425932465965236</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-1.42805094022607</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.604088422287247</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.262803220280373</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.96752975420509</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.759119774817883</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.12071946829983</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.728415839645262</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-1.2958581568891</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.481164064170337</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.810134362961151</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-1.1974812755319</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-1.87848402126128</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.191862543598763</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.439414807919103</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.590819929001823</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.441030659961037</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.01707541756539</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.510016750200758</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.125656779120664</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.229215105572592</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-1.71984014290537</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-1.18469356022401</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.118556484275384</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.25188668987019</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.232524014261435</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.794163386868499</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1.10846514110633</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.440696223829333</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-1.36588993581575</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.71990149787111</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1.55020878849321</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1.86786272696106</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.886133063518687</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.996097751215611</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.64978268596428</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.0911769113846916</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.1846443765872</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.0833462980561341</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.791816464648993</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.0531639449510776</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.350209566691383</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.291368784274084</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.385996124157857</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-1.26704269907209</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.370834411591228</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.188891814255598</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-1.24219105787728</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-1.97323745260169</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.842075305331894</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.54798145889829</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.281176611265745</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.294519673042499</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.821861560820602</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.642936545818244</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.396969855772144</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.0256168308408748</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.10451657921262</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.105497783597355</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.957291576922202</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
